--- a/public/data/contracts.xlsx
+++ b/public/data/contracts.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,13 +442,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>8804be40-aa6d-4db8-8332-6c0383240a8d</v>
+        <v>c0f92e8a-aa8b-4aa2-bec2-95cb55998bf6</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001</v>
@@ -460,10 +460,10 @@
         <v>TMA101</v>
       </c>
       <c r="G2" t="str">
-        <v>59d80d33-537e-4a37-8655-1739660ec5d4</v>
+        <v>3878f7f2-c5c5-48c0-9178-4fed0b5ffef5</v>
       </c>
       <c r="H2" t="str">
-        <v>53bca1fc-519c-458e-91f3-f73ab9c834fe</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="I2" t="str">
         <v>CTR-001-001</v>
@@ -475,7 +475,7 @@
         <v>2025-01-01</v>
       </c>
       <c r="L2" t="str">
-        <v>2025-12-31</v>
+        <v>2026-03-01</v>
       </c>
       <c r="M2" t="str">
         <v>Exclusive Seaplane (Day time)</v>
@@ -483,163 +483,163 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>3ca3e100-c368-43ff-a72b-9575ae13adf2</v>
+        <v>78cd917a-a41b-4df3-8a31-0015a170155d</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
-        <v>CTR-002</v>
+        <v>CTR-001</v>
       </c>
       <c r="E3" t="str">
-        <v>MAR-SRV-2025</v>
+        <v>MAR-WAI-2025</v>
       </c>
       <c r="F3" t="str">
         <v>TMA101</v>
       </c>
       <c r="G3" t="str">
-        <v>59d80d33-537e-4a37-8655-1739660ec5d4</v>
+        <v>3878f7f2-c5c5-48c0-9178-4fed0b5ffef5</v>
       </c>
       <c r="H3" t="str">
-        <v>819129ff-9f49-45d0-92b3-d595220fdfb5</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="I3" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="J3" t="str">
-        <v>Transfer</v>
+        <v>Charter</v>
       </c>
       <c r="K3" t="str">
-        <v>2025-03-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-28</v>
+        <v>2026-05-31</v>
       </c>
       <c r="M3" t="str">
-        <v>Exclusive Seaplane (Day time)</v>
+        <v>Charter Agreement</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>8460e4e7-8321-4274-b1fa-e7828dd88619</v>
+        <v>b9037295-b281-4339-9c92-58351d8b0574</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-003</v>
+        <v>CTR-002</v>
       </c>
       <c r="E4" t="str">
-        <v>SON-SF-2025</v>
+        <v>MAR-SRV-2025</v>
       </c>
       <c r="F4" t="str">
         <v>TMA101</v>
       </c>
       <c r="G4" t="str">
-        <v>13d45613-2988-4ea6-80b8-5f95f812cfb4</v>
+        <v>3878f7f2-c5c5-48c0-9178-4fed0b5ffef5</v>
       </c>
       <c r="H4" t="str">
-        <v>99492203-f941-48e8-923d-076e492f5230</v>
+        <v>42e6bcee-426a-4f7a-877e-20c9962142d5</v>
       </c>
       <c r="I4" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="J4" t="str">
-        <v>Charter</v>
+        <v>Transfer</v>
       </c>
       <c r="K4" t="str">
-        <v>2025-06-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-05-31</v>
+        <v>2027-02-28</v>
       </c>
       <c r="M4" t="str">
-        <v>Charter Agreement</v>
+        <v>Exclusive Seaplane (Day time)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>c46c84c4-734a-4a60-b97e-9b98b863dab9</v>
+        <v>a88b36f6-364e-4b60-974f-222c0081fc60</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-004</v>
+        <v>CTR-003</v>
       </c>
       <c r="E5" t="str">
-        <v>LVMH-CBR-2025</v>
+        <v>SON-SF-2025</v>
       </c>
       <c r="F5" t="str">
         <v>TMA101</v>
       </c>
       <c r="G5" t="str">
-        <v>49848a44-2a6a-4193-8607-c2ca1897d7a7</v>
+        <v>777dac53-12bf-48ef-a913-ac3e14639321</v>
       </c>
       <c r="H5" t="str">
-        <v>ae61d497-ed25-4ed3-b6f5-07f017123cbd</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="I5" t="str">
-        <v>CTR-004-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="J5" t="str">
-        <v>Signed Charter</v>
+        <v>Charter</v>
       </c>
       <c r="K5" t="str">
-        <v>2024-01-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="L5" t="str">
-        <v>2024-12-31</v>
+        <v>2027-05-31</v>
       </c>
       <c r="M5" t="str">
-        <v>Signed Charter Agreement</v>
+        <v>Charter Agreement</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>18074a3c-28d1-4af9-bfcb-729b210cc637</v>
+        <v>2d49a8f8-7dad-441d-a2fe-0ac431ddd8e5</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-005</v>
+        <v>CTR-003</v>
       </c>
       <c r="E6" t="str">
-        <v>MAR-PMF-2025</v>
+        <v>SON-SF-2025</v>
       </c>
       <c r="F6" t="str">
         <v>TMA101</v>
       </c>
       <c r="G6" t="str">
-        <v>59d80d33-537e-4a37-8655-1739660ec5d4</v>
+        <v>777dac53-12bf-48ef-a913-ac3e14639321</v>
       </c>
       <c r="H6" t="str">
-        <v>44e8275f-6dbf-4a68-8aa8-3a6a09ecac5e</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="I6" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="J6" t="str">
         <v>Transfer</v>
       </c>
       <c r="K6" t="str">
-        <v>2025-04-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-03-31</v>
+        <v>2026-12-31</v>
       </c>
       <c r="M6" t="str">
         <v>Exclusive Seaplane (Day time)</v>
@@ -647,157 +647,157 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>56914a2b-bd6a-418c-8e32-4b7bf224404c</v>
+        <v>ac4463fc-0f11-4250-a7d1-ee3d343e1431</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-006</v>
+        <v>CTR-003</v>
       </c>
       <c r="E7" t="str">
-        <v>FS-FSLG-2026</v>
+        <v>SON-SF-2025</v>
       </c>
       <c r="F7" t="str">
         <v>TMA101</v>
       </c>
       <c r="G7" t="str">
-        <v>fa50e21f-d5b2-4543-8b76-17007d80b959</v>
+        <v>777dac53-12bf-48ef-a913-ac3e14639321</v>
       </c>
       <c r="H7" t="str">
-        <v>c4b72dfb-694a-4cd6-a5be-cb1bddcaa2a5</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="I7" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="J7" t="str">
-        <v>Transfer</v>
+        <v>Signed Charter</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-01-01</v>
+        <v>2025-10-01</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-12-31</v>
+        <v>2026-09-30</v>
       </c>
       <c r="M7" t="str">
-        <v>Exclusive Seaplane (Day time)</v>
+        <v>Signed Charter Agreement</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>972c7ed7-e881-472b-b5b8-3308c95bbfe7</v>
+        <v>9a4b1770-6a3e-42c5-b683-6bae0cafa620</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-007</v>
+        <v>CTR-004</v>
       </c>
       <c r="E8" t="str">
-        <v>FS-FSKH-2025</v>
+        <v>LVMH-CBR-2024</v>
       </c>
       <c r="F8" t="str">
         <v>TMA101</v>
       </c>
       <c r="G8" t="str">
-        <v>fa50e21f-d5b2-4543-8b76-17007d80b959</v>
+        <v>2d720ce4-b7e5-4a56-bebe-46ba7ddefe65</v>
       </c>
       <c r="H8" t="str">
-        <v>9fda538c-f70f-447b-9d9a-f641700abf98</v>
+        <v>c4b758b0-8279-41c1-9617-c33355bf329a</v>
       </c>
       <c r="I8" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-004-001</v>
       </c>
       <c r="J8" t="str">
-        <v>Transfer</v>
+        <v>Signed Charter</v>
       </c>
       <c r="K8" t="str">
-        <v>2025-01-01</v>
+        <v>2024-01-01</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-03-10</v>
+        <v>2024-12-31</v>
       </c>
       <c r="M8" t="str">
-        <v>Exclusive Seaplane (Day time)</v>
+        <v>Signed Charter Agreement</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>f99c4af2-4b31-460a-ba00-3d940a1db42e</v>
+        <v>8003b4e4-5d86-4a0e-90e2-d92850a7b277</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-008</v>
+        <v>CTR-005</v>
       </c>
       <c r="E9" t="str">
-        <v>MINT-AKV-2026</v>
+        <v>MAR-PMF-2025</v>
       </c>
       <c r="F9" t="str">
         <v>TMA101</v>
       </c>
       <c r="G9" t="str">
-        <v>e9ce8fb9-566a-4b6e-88e6-012467e48a71</v>
+        <v>3878f7f2-c5c5-48c0-9178-4fed0b5ffef5</v>
       </c>
       <c r="H9" t="str">
-        <v>79958ed2-9c5b-421b-98f3-26062254d840</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="I9" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="J9" t="str">
-        <v>Charter</v>
+        <v>Transfer</v>
       </c>
       <c r="K9" t="str">
-        <v>2025-10-01</v>
+        <v>2025-04-01</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-09-30</v>
+        <v>2027-03-31</v>
       </c>
       <c r="M9" t="str">
-        <v>Charter Agreement</v>
+        <v>Exclusive Seaplane (Day time)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0c9f09d7-c165-40f2-bf66-c025930d9a46</v>
+        <v>acc61d98-766d-4699-824b-8957c82e9880</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-009</v>
+        <v>CTR-005</v>
       </c>
       <c r="E10" t="str">
-        <v>MAR-RCFI-2026</v>
+        <v>MAR-PMF-2025</v>
       </c>
       <c r="F10" t="str">
         <v>TMA101</v>
       </c>
       <c r="G10" t="str">
-        <v>59d80d33-537e-4a37-8655-1739660ec5d4</v>
+        <v>3878f7f2-c5c5-48c0-9178-4fed0b5ffef5</v>
       </c>
       <c r="H10" t="str">
-        <v>28f29363-bd63-4176-95b1-4de2fd79edf4</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="I10" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="J10" t="str">
-        <v>Transfer</v>
+        <v>Charter</v>
       </c>
       <c r="K10" t="str">
         <v>2025-11-01</v>
@@ -806,53 +806,422 @@
         <v>2026-10-31</v>
       </c>
       <c r="M10" t="str">
-        <v>Exclusive Seaplane (Day time)</v>
+        <v>Charter Agreement</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>a475ecad-2589-4b10-b614-551819a228d4</v>
+        <v>6d461192-db6a-452f-b9da-1b11c9a51892</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
+        <v>CTR-006</v>
+      </c>
+      <c r="E11" t="str">
+        <v>FS-FSLG-2025</v>
+      </c>
+      <c r="F11" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G11" t="str">
+        <v>b90a2822-5146-4bc6-8193-1413cd5a2e04</v>
+      </c>
+      <c r="H11" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="I11" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2025-01-01</v>
+      </c>
+      <c r="L11" t="str">
+        <v>2027-12-31</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Exclusive Seaplane (Day time)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>854f50a4-31dc-44ba-80b4-78507bca3ef4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D12" t="str">
+        <v>CTR-006</v>
+      </c>
+      <c r="E12" t="str">
+        <v>FS-FSLG-2025</v>
+      </c>
+      <c r="F12" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G12" t="str">
+        <v>b90a2822-5146-4bc6-8193-1413cd5a2e04</v>
+      </c>
+      <c r="H12" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="I12" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Charter</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2025-06-01</v>
+      </c>
+      <c r="L12" t="str">
+        <v>2027-05-31</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Charter Agreement</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>9060cc4e-5de5-426c-a394-8306393b1b09</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D13" t="str">
+        <v>CTR-006</v>
+      </c>
+      <c r="E13" t="str">
+        <v>FS-FSLG-2025</v>
+      </c>
+      <c r="F13" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G13" t="str">
+        <v>b90a2822-5146-4bc6-8193-1413cd5a2e04</v>
+      </c>
+      <c r="H13" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="I13" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Signed Charter</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-12-31</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Signed Charter Agreement</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>751a7f5c-6eb1-4059-a3f3-28923fbed286</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D14" t="str">
+        <v>CTR-007</v>
+      </c>
+      <c r="E14" t="str">
+        <v>FS-FSKH-2025</v>
+      </c>
+      <c r="F14" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G14" t="str">
+        <v>b90a2822-5146-4bc6-8193-1413cd5a2e04</v>
+      </c>
+      <c r="H14" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="I14" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2025-01-01</v>
+      </c>
+      <c r="L14" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Exclusive Speedboat</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5e23c4f6-3282-4a58-ae5a-03461ceb868d</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CTR-007</v>
+      </c>
+      <c r="E15" t="str">
+        <v>FS-FSKH-2025</v>
+      </c>
+      <c r="F15" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G15" t="str">
+        <v>b90a2822-5146-4bc6-8193-1413cd5a2e04</v>
+      </c>
+      <c r="H15" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="I15" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2025-01-01</v>
+      </c>
+      <c r="L15" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Exclusive Seaplane (Day time)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>b015f249-d107-4b91-a15a-f882a23c73a6</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CTR-008</v>
+      </c>
+      <c r="E16" t="str">
+        <v>MINT-AKV-2025</v>
+      </c>
+      <c r="F16" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G16" t="str">
+        <v>00814f5b-b883-4ca7-b853-b2667ab37505</v>
+      </c>
+      <c r="H16" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="I16" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Charter</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="L16" t="str">
+        <v>2027-09-30</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Charter Agreement</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>593fada6-c6da-4a28-bd27-28a0ada37389</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-008</v>
+      </c>
+      <c r="E17" t="str">
+        <v>MINT-AKV-2025</v>
+      </c>
+      <c r="F17" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G17" t="str">
+        <v>00814f5b-b883-4ca7-b853-b2667ab37505</v>
+      </c>
+      <c r="H17" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="I17" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="L17" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Exclusive Seaplane (Day time)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>04bb15d6-9e8a-4631-b7e7-04dae158c4d2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CTR-009</v>
+      </c>
+      <c r="E18" t="str">
+        <v>MAR-RCFI-2026</v>
+      </c>
+      <c r="F18" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G18" t="str">
+        <v>3878f7f2-c5c5-48c0-9178-4fed0b5ffef5</v>
+      </c>
+      <c r="H18" t="str">
+        <v>7a7a2625-26bd-424d-acbe-9c84fc54ea85</v>
+      </c>
+      <c r="I18" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2025-11-01</v>
+      </c>
+      <c r="L18" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Exclusive Speedboat</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>daca0df5-90b1-426b-b6e8-4afd695e1cd0</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
         <v>CTR-010</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E19" t="str">
         <v>SON-SJ-2024</v>
       </c>
-      <c r="F11" t="str">
-        <v>TMA101</v>
-      </c>
-      <c r="G11" t="str">
-        <v>13d45613-2988-4ea6-80b8-5f95f812cfb4</v>
-      </c>
-      <c r="H11" t="str">
-        <v>b2c6555b-31b8-470c-a25d-e7b05dadb044</v>
-      </c>
-      <c r="I11" t="str">
+      <c r="F19" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G19" t="str">
+        <v>777dac53-12bf-48ef-a913-ac3e14639321</v>
+      </c>
+      <c r="H19" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="I19" t="str">
         <v>CTR-010-001</v>
       </c>
-      <c r="J11" t="str">
+      <c r="J19" t="str">
         <v>Charter</v>
       </c>
-      <c r="K11" t="str">
+      <c r="K19" t="str">
         <v>2024-03-01</v>
       </c>
-      <c r="L11" t="str">
+      <c r="L19" t="str">
         <v>2025-02-28</v>
       </c>
-      <c r="M11" t="str">
+      <c r="M19" t="str">
         <v>Charter Agreement</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>7e24aec1-1b96-44df-bfc4-b54406625ab0</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CTR-010</v>
+      </c>
+      <c r="E20" t="str">
+        <v>SON-SJ-2024</v>
+      </c>
+      <c r="F20" t="str">
+        <v>TMA101</v>
+      </c>
+      <c r="G20" t="str">
+        <v>777dac53-12bf-48ef-a913-ac3e14639321</v>
+      </c>
+      <c r="H20" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="I20" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2024-03-01</v>
+      </c>
+      <c r="L20" t="str">
+        <v>2025-02-28</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Exclusive Seaplane (Day time)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M20"/>
   </ignoredErrors>
 </worksheet>
 </file>